--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run10/epoch_70/per_file_predictions_epoch_70.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run10/epoch_70/per_file_predictions_epoch_70.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.6899,0.0142,0.3091,0.0238</t>
-  </si>
-  <si>
-    <t>0.0213,0.0023,0.0029,0.9878</t>
-  </si>
-  <si>
-    <t>0.8908,0.0104,0.0044,0.0799</t>
-  </si>
-  <si>
-    <t>0.0737,0.0270,0.0057,0.9639</t>
-  </si>
-  <si>
-    <t>0.9918,0.0072,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9949,0.0017,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9912,0.0085,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.9896,0.0074,0.0004,0.0009</t>
-  </si>
-  <si>
-    <t>0.9847,0.0119,0.0007,0.0017</t>
-  </si>
-  <si>
-    <t>0.9843,0.0200,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.9965,0.0010,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9930,0.0031,0.0007,0.0010</t>
-  </si>
-  <si>
-    <t>0.7872,0.1572,0.0759,0.0111</t>
-  </si>
-  <si>
-    <t>0.1876,0.0046,0.8995,0.0013</t>
-  </si>
-  <si>
-    <t>0.6980,0.1156,0.2144,0.0093</t>
-  </si>
-  <si>
-    <t>0.1567,0.0074,0.9020,0.0009</t>
-  </si>
-  <si>
-    <t>0.7068,0.0282,0.3365,0.0046</t>
-  </si>
-  <si>
-    <t>0.0013,0.9970,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0041,0.9931,0.0019,0.0003</t>
-  </si>
-  <si>
-    <t>0.4840,0.6492,0.0051,0.0008</t>
-  </si>
-  <si>
-    <t>0.0199,0.9771,0.0029,0.0004</t>
-  </si>
-  <si>
-    <t>0.0117,0.9812,0.0098,0.0007</t>
-  </si>
-  <si>
-    <t>0.7702,0.0133,0.2451,0.0022</t>
-  </si>
-  <si>
-    <t>0.3046,0.0155,0.7380,0.0125</t>
-  </si>
-  <si>
-    <t>0.0121,0.0257,0.9703,0.0049</t>
-  </si>
-  <si>
-    <t>0.0499,0.0108,0.9572,0.0012</t>
-  </si>
-  <si>
-    <t>0.0262,0.0054,0.9687,0.0044</t>
-  </si>
-  <si>
-    <t>0.0201,0.0051,0.9652,0.0097</t>
-  </si>
-  <si>
-    <t>0.0103,0.0151,0.9649,0.0351</t>
-  </si>
-  <si>
-    <t>0.7245,0.2932,0.0525,0.0053</t>
-  </si>
-  <si>
-    <t>0.5302,0.0973,0.5128,0.0076</t>
-  </si>
-  <si>
-    <t>0.0124,0.0108,0.9816,0.0038</t>
-  </si>
-  <si>
-    <t>0.0162,0.9405,0.0711,0.0006</t>
-  </si>
-  <si>
-    <t>0.9366,0.0322,0.0067,0.0071</t>
-  </si>
-  <si>
-    <t>0.5579,0.1409,0.3576,0.0126</t>
-  </si>
-  <si>
-    <t>0.7712,0.3420,0.0076,0.0024</t>
-  </si>
-  <si>
-    <t>0.0269,0.9200,0.2550,0.0013</t>
-  </si>
-  <si>
-    <t>0.0891,0.7247,0.2166,0.0724</t>
-  </si>
-  <si>
-    <t>0.0628,0.2206,0.8724,0.0064</t>
-  </si>
-  <si>
-    <t>0.1006,0.2265,0.8257,0.0092</t>
-  </si>
-  <si>
-    <t>0.3797,0.0071,0.3767,0.1371</t>
-  </si>
-  <si>
-    <t>0.0836,0.1584,0.8558,0.0046</t>
-  </si>
-  <si>
-    <t>0.0093,0.9663,0.0461,0.0002</t>
-  </si>
-  <si>
-    <t>0.0711,0.1568,0.8250,0.0225</t>
-  </si>
-  <si>
-    <t>0.2288,0.3262,0.0082,0.6311</t>
-  </si>
-  <si>
-    <t>0.0056,0.9767,0.0092,0.0063</t>
-  </si>
-  <si>
-    <t>0.0030,0.9851,0.0449,0.0010</t>
-  </si>
-  <si>
-    <t>0.0015,0.9934,0.0178,0.0003</t>
-  </si>
-  <si>
-    <t>0.0033,0.0132,0.9882,0.0019</t>
-  </si>
-  <si>
-    <t>0.0164,0.0546,0.9704,0.0005</t>
-  </si>
-  <si>
-    <t>0.2117,0.0300,0.8434,0.0088</t>
-  </si>
-  <si>
-    <t>0.2032,0.0042,0.8211,0.0149</t>
-  </si>
-  <si>
-    <t>0.0113,0.0049,0.9832,0.0085</t>
-  </si>
-  <si>
-    <t>0.0037,0.0121,0.9925,0.0008</t>
-  </si>
-  <si>
-    <t>0.9669,0.0280,0.0044,0.0017</t>
-  </si>
-  <si>
-    <t>0.9750,0.0206,0.0031,0.0017</t>
-  </si>
-  <si>
-    <t>0.9838,0.0190,0.0008,0.0009</t>
-  </si>
-  <si>
-    <t>0.0062,0.3254,0.9720,0.0005</t>
-  </si>
-  <si>
-    <t>0.9938,0.0051,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9876,0.0086,0.0012,0.0009</t>
-  </si>
-  <si>
-    <t>0.9625,0.0586,0.0026,0.0007</t>
-  </si>
-  <si>
-    <t>0.0038,0.6928,0.9359,0.0017</t>
-  </si>
-  <si>
-    <t>0.0022,0.0094,0.9850,0.0085</t>
-  </si>
-  <si>
-    <t>0.0025,0.0435,0.9813,0.0085</t>
-  </si>
-  <si>
-    <t>0.0011,0.5800,0.9881,0.0001</t>
-  </si>
-  <si>
-    <t>0.0032,0.0056,0.9917,0.0023</t>
-  </si>
-  <si>
-    <t>0.0156,0.9220,0.4254,0.0010</t>
-  </si>
-  <si>
-    <t>0.0162,0.9796,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.7674,0.0209,0.2949,0.0023</t>
-  </si>
-  <si>
-    <t>0.7399,0.3037,0.0246,0.0081</t>
-  </si>
-  <si>
-    <t>0.0215,0.0213,0.9687,0.0040</t>
-  </si>
-  <si>
-    <t>0.0029,0.9211,0.5743,0.0004</t>
-  </si>
-  <si>
-    <t>0.0030,0.9659,0.3094,0.0004</t>
-  </si>
-  <si>
-    <t>0.0010,0.9923,0.0861,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.9486,0.9170,0.0001</t>
-  </si>
-  <si>
-    <t>0.0523,0.0198,0.0337,0.9395</t>
-  </si>
-  <si>
-    <t>0.0049,0.0008,0.0004,0.9976</t>
-  </si>
-  <si>
-    <t>0.0070,0.0026,0.0010,0.9951</t>
-  </si>
-  <si>
-    <t>0.0234,0.0014,0.0074,0.9804</t>
-  </si>
-  <si>
-    <t>0.1071,0.0126,0.0035,0.9548</t>
-  </si>
-  <si>
-    <t>0.0094,0.0006,0.0023,0.9932</t>
-  </si>
-  <si>
-    <t>0.0004,0.9755,0.7851,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.5051,0.9873,0.0000</t>
-  </si>
-  <si>
-    <t>0.0089,0.8311,0.4211,0.0047</t>
-  </si>
-  <si>
-    <t>0.0248,0.1965,0.9246,0.0054</t>
-  </si>
-  <si>
-    <t>0.0006,0.9755,0.6674,0.0000</t>
-  </si>
-  <si>
-    <t>0.0067,0.8047,0.6120,0.0010</t>
-  </si>
-  <si>
-    <t>0.9871,0.0112,0.0006,0.0010</t>
-  </si>
-  <si>
-    <t>0.9682,0.0374,0.0020,0.0012</t>
-  </si>
-  <si>
-    <t>0.9841,0.0243,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.9943,0.0010,0.0002,0.0016</t>
-  </si>
-  <si>
-    <t>0.9876,0.0110,0.0005,0.0010</t>
-  </si>
-  <si>
-    <t>0.9934,0.0022,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.9826,0.0115,0.0013,0.0025</t>
-  </si>
-  <si>
-    <t>0.9874,0.0100,0.0019,0.0006</t>
-  </si>
-  <si>
-    <t>0.9952,0.0020,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9950,0.0014,0.0001,0.0009</t>
-  </si>
-  <si>
-    <t>0.9950,0.0023,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9976,0.0005,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9942,0.0038,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9918,0.0040,0.0009,0.0009</t>
-  </si>
-  <si>
-    <t>0.9901,0.0037,0.0005,0.0018</t>
-  </si>
-  <si>
-    <t>0.9935,0.0037,0.0006,0.0006</t>
-  </si>
-  <si>
-    <t>0.0205,0.0031,0.9710,0.0132</t>
-  </si>
-  <si>
-    <t>0.1360,0.0226,0.8682,0.0016</t>
-  </si>
-  <si>
-    <t>0.8363,0.0111,0.1389,0.0155</t>
-  </si>
-  <si>
-    <t>0.1051,0.0039,0.9315,0.0025</t>
-  </si>
-  <si>
-    <t>0.0381,0.9557,0.0094,0.0011</t>
-  </si>
-  <si>
-    <t>0.0335,0.9644,0.0035,0.0009</t>
-  </si>
-  <si>
-    <t>0.1220,0.9042,0.0024,0.0015</t>
-  </si>
-  <si>
-    <t>0.0715,0.9329,0.0039,0.0012</t>
-  </si>
-  <si>
-    <t>0.0306,0.9569,0.0046,0.0021</t>
-  </si>
-  <si>
-    <t>0.0043,0.9919,0.0006,0.0006</t>
-  </si>
-  <si>
-    <t>0.7957,0.3101,0.0042,0.0006</t>
-  </si>
-  <si>
-    <t>0.5737,0.0327,0.3552,0.0567</t>
-  </si>
-  <si>
-    <t>0.5724,0.0083,0.5296,0.0035</t>
-  </si>
-  <si>
-    <t>0.4925,0.3527,0.2274,0.0777</t>
-  </si>
-  <si>
-    <t>0.6325,0.0557,0.3681,0.0083</t>
-  </si>
-  <si>
-    <t>0.1653,0.1055,0.0114,0.8280</t>
-  </si>
-  <si>
-    <t>0.0036,0.9785,0.0121,0.0061</t>
-  </si>
-  <si>
-    <t>0.0017,0.9617,0.0047,0.1438</t>
-  </si>
-  <si>
-    <t>0.0073,0.9745,0.0057,0.0282</t>
-  </si>
-  <si>
-    <t>0.0019,0.9384,0.8220,0.0006</t>
-  </si>
-  <si>
-    <t>0.0065,0.9846,0.0362,0.0002</t>
-  </si>
-  <si>
-    <t>0.8199,0.2744,0.0076,0.0006</t>
-  </si>
-  <si>
-    <t>0.8667,0.1739,0.0126,0.0013</t>
-  </si>
-  <si>
-    <t>0.9893,0.0112,0.0010,0.0004</t>
-  </si>
-  <si>
-    <t>0.9883,0.0036,0.0017,0.0018</t>
-  </si>
-  <si>
-    <t>0.9890,0.0025,0.0010,0.0025</t>
-  </si>
-  <si>
-    <t>0.9970,0.0009,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9973,0.0004,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9895,0.0067,0.0021,0.0006</t>
-  </si>
-  <si>
-    <t>0.9803,0.0080,0.0041,0.0031</t>
-  </si>
-  <si>
-    <t>0.9835,0.0065,0.0013,0.0032</t>
-  </si>
-  <si>
-    <t>0.0017,0.6858,0.9480,0.0002</t>
-  </si>
-  <si>
-    <t>0.0178,0.3022,0.8426,0.0004</t>
-  </si>
-  <si>
-    <t>0.0084,0.4261,0.9002,0.0016</t>
-  </si>
-  <si>
-    <t>0.0697,0.0259,0.9196,0.0031</t>
-  </si>
-  <si>
-    <t>0.6613,0.2056,0.0520,0.0980</t>
-  </si>
-  <si>
-    <t>0.8594,0.0341,0.0816,0.0190</t>
-  </si>
-  <si>
-    <t>0.2787,0.0074,0.7681,0.0145</t>
-  </si>
-  <si>
-    <t>0.7058,0.1209,0.2108,0.0170</t>
-  </si>
-  <si>
-    <t>0.1490,0.0165,0.0095,0.9232</t>
-  </si>
-  <si>
-    <t>0.0012,0.0007,0.0013,0.9983</t>
-  </si>
-  <si>
-    <t>0.0124,0.0075,0.0044,0.9898</t>
-  </si>
-  <si>
-    <t>0.0018,0.0001,0.0022,0.9977</t>
-  </si>
-  <si>
-    <t>0.0027,0.7975,0.8920,0.0008</t>
-  </si>
-  <si>
-    <t>0.9872,0.0056,0.0007,0.0017</t>
-  </si>
-  <si>
-    <t>0.2332,0.8242,0.0060,0.0019</t>
-  </si>
-  <si>
-    <t>0.9836,0.0057,0.0010,0.0032</t>
-  </si>
-  <si>
-    <t>0.3495,0.7251,0.0125,0.0010</t>
-  </si>
-  <si>
-    <t>0.9820,0.0050,0.0017,0.0031</t>
-  </si>
-  <si>
-    <t>0.8876,0.0318,0.0188,0.0443</t>
-  </si>
-  <si>
-    <t>0.9816,0.0039,0.0016,0.0044</t>
-  </si>
-  <si>
-    <t>0.0009,0.0161,0.9899,0.0062</t>
-  </si>
-  <si>
-    <t>0.8273,0.0019,0.0043,0.2048</t>
-  </si>
-  <si>
-    <t>0.9445,0.0216,0.0134,0.0121</t>
-  </si>
-  <si>
-    <t>0.2808,0.7680,0.0218,0.0040</t>
-  </si>
-  <si>
-    <t>0.9421,0.0328,0.0189,0.0021</t>
-  </si>
-  <si>
-    <t>0.9026,0.0924,0.0225,0.0020</t>
-  </si>
-  <si>
-    <t>0.1185,0.7941,0.1478,0.0470</t>
-  </si>
-  <si>
-    <t>0.8809,0.0760,0.0490,0.0079</t>
-  </si>
-  <si>
-    <t>0.8431,0.0846,0.0570,0.0084</t>
-  </si>
-  <si>
-    <t>0.9941,0.0007,0.0003,0.0020</t>
-  </si>
-  <si>
-    <t>0.9940,0.0025,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.9907,0.0024,0.0002,0.0016</t>
-  </si>
-  <si>
-    <t>0.9914,0.0016,0.0007,0.0019</t>
-  </si>
-  <si>
-    <t>0.9898,0.0027,0.0014,0.0019</t>
-  </si>
-  <si>
-    <t>0.9757,0.0107,0.0042,0.0027</t>
-  </si>
-  <si>
-    <t>0.9930,0.0026,0.0005,0.0012</t>
-  </si>
-  <si>
-    <t>0.9925,0.0017,0.0009,0.0014</t>
-  </si>
-  <si>
-    <t>0.8538,0.2165,0.0042,0.0024</t>
-  </si>
-  <si>
-    <t>0.6973,0.4314,0.0072,0.0004</t>
-  </si>
-  <si>
-    <t>0.6033,0.5607,0.0013,0.0003</t>
-  </si>
-  <si>
-    <t>0.9065,0.1130,0.0117,0.0073</t>
-  </si>
-  <si>
-    <t>0.9731,0.0304,0.0011,0.0013</t>
-  </si>
-  <si>
-    <t>0.8446,0.1605,0.0261,0.0080</t>
-  </si>
-  <si>
-    <t>0.9450,0.0779,0.0060,0.0014</t>
-  </si>
-  <si>
-    <t>0.9342,0.0810,0.0082,0.0008</t>
-  </si>
-  <si>
-    <t>0.0265,0.0075,0.9823,0.0008</t>
-  </si>
-  <si>
-    <t>0.9654,0.0508,0.0012,0.0006</t>
-  </si>
-  <si>
-    <t>0.0089,0.0059,0.9907,0.0003</t>
-  </si>
-  <si>
-    <t>0.0091,0.0952,0.9424,0.0139</t>
-  </si>
-  <si>
-    <t>0.1082,0.0040,0.9359,0.0033</t>
-  </si>
-  <si>
-    <t>0.0247,0.0358,0.9636,0.0040</t>
-  </si>
-  <si>
-    <t>0.0302,0.0302,0.9623,0.0023</t>
-  </si>
-  <si>
-    <t>0.0088,0.0011,0.9926,0.0008</t>
-  </si>
-  <si>
-    <t>0.0176,0.0054,0.9751,0.0037</t>
-  </si>
-  <si>
-    <t>0.6293,0.2112,0.2126,0.0273</t>
-  </si>
-  <si>
-    <t>0.4981,0.0244,0.5836,0.0049</t>
-  </si>
-  <si>
-    <t>0.2083,0.0231,0.8257,0.0146</t>
-  </si>
-  <si>
-    <t>0.0978,0.1688,0.6862,0.0019</t>
-  </si>
-  <si>
-    <t>0.3863,0.0219,0.7324,0.0017</t>
-  </si>
-  <si>
-    <t>0.4601,0.0802,0.5063,0.0074</t>
-  </si>
-  <si>
-    <t>0.7698,0.0582,0.1605,0.0302</t>
-  </si>
-  <si>
-    <t>0.4649,0.0415,0.5648,0.0293</t>
-  </si>
-  <si>
-    <t>0.6423,0.5201,0.0041,0.0004</t>
-  </si>
-  <si>
-    <t>0.5507,0.6081,0.0032,0.0004</t>
-  </si>
-  <si>
-    <t>0.5992,0.4715,0.0201,0.0023</t>
-  </si>
-  <si>
-    <t>0.9547,0.0802,0.0021,0.0007</t>
-  </si>
-  <si>
-    <t>0.9740,0.0474,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.6196,0.2197,0.1902,0.0302</t>
-  </si>
-  <si>
-    <t>0.6982,0.0106,0.3957,0.0023</t>
-  </si>
-  <si>
-    <t>0.7876,0.0119,0.1545,0.0273</t>
-  </si>
-  <si>
-    <t>0.8442,0.0078,0.1392,0.0075</t>
-  </si>
-  <si>
-    <t>0.8194,0.0356,0.1025,0.0319</t>
-  </si>
-  <si>
-    <t>0.0139,0.0032,0.9760,0.0126</t>
-  </si>
-  <si>
-    <t>0.0518,0.0779,0.8955,0.0190</t>
-  </si>
-  <si>
-    <t>0.0133,0.3755,0.9317,0.0028</t>
-  </si>
-  <si>
-    <t>0.1067,0.0491,0.8539,0.0317</t>
-  </si>
-  <si>
-    <t>0.0618,0.0126,0.9342,0.0021</t>
-  </si>
-  <si>
-    <t>0.9950,0.0014,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9823,0.0135,0.0032,0.0013</t>
-  </si>
-  <si>
-    <t>0.9905,0.0063,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9916,0.0046,0.0008,0.0009</t>
-  </si>
-  <si>
-    <t>0.9639,0.0365,0.0022,0.0026</t>
-  </si>
-  <si>
-    <t>0.9839,0.0084,0.0011,0.0026</t>
-  </si>
-  <si>
-    <t>0.9967,0.0008,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9945,0.0021,0.0004,0.0008</t>
-  </si>
-  <si>
-    <t>0.0505,0.0111,0.9567,0.0033</t>
-  </si>
-  <si>
-    <t>0.5922,0.1439,0.3446,0.0153</t>
-  </si>
-  <si>
-    <t>0.9581,0.0225,0.0080,0.0050</t>
-  </si>
-  <si>
-    <t>0.0022,0.0056,0.9931,0.0044</t>
-  </si>
-  <si>
-    <t>0.0024,0.0133,0.9854,0.0094</t>
-  </si>
-  <si>
-    <t>0.0158,0.0495,0.9519,0.0017</t>
-  </si>
-  <si>
-    <t>0.0009,0.0047,0.9957,0.0027</t>
-  </si>
-  <si>
-    <t>0.0979,0.0646,0.8205,0.0193</t>
-  </si>
-  <si>
-    <t>0.0035,0.0832,0.9890,0.0004</t>
-  </si>
-  <si>
-    <t>0.0116,0.0025,0.9842,0.0024</t>
-  </si>
-  <si>
-    <t>0.1794,0.0159,0.8346,0.0096</t>
-  </si>
-  <si>
-    <t>0.7151,0.0760,0.2149,0.0155</t>
-  </si>
-  <si>
-    <t>0.8698,0.0065,0.1148,0.0083</t>
-  </si>
-  <si>
-    <t>0.8504,0.0103,0.0770,0.0271</t>
-  </si>
-  <si>
-    <t>0.9766,0.0142,0.0013,0.0042</t>
-  </si>
-  <si>
-    <t>0.9891,0.0060,0.0015,0.0010</t>
-  </si>
-  <si>
-    <t>0.9955,0.0033,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9838,0.0139,0.0010,0.0010</t>
-  </si>
-  <si>
-    <t>0.9951,0.0038,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9755,0.0318,0.0023,0.0008</t>
-  </si>
-  <si>
-    <t>0.9934,0.0031,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.9872,0.0040,0.0007,0.0031</t>
-  </si>
-  <si>
-    <t>0.1203,0.1245,0.7887,0.0049</t>
-  </si>
-  <si>
-    <t>0.0049,0.0957,0.9851,0.0009</t>
-  </si>
-  <si>
-    <t>0.0210,0.1171,0.9275,0.0091</t>
-  </si>
-  <si>
-    <t>0.2742,0.0469,0.7314,0.0103</t>
-  </si>
-  <si>
-    <t>0.0420,0.0035,0.9719,0.0021</t>
-  </si>
-  <si>
-    <t>0.2768,0.0547,0.1212,0.6108</t>
-  </si>
-  <si>
-    <t>0.0842,0.0067,0.8928,0.0258</t>
-  </si>
-  <si>
-    <t>0.1501,0.0952,0.7840,0.0036</t>
-  </si>
-  <si>
-    <t>0.9486,0.0045,0.0069,0.0368</t>
-  </si>
-  <si>
-    <t>0.0380,0.0640,0.0038,0.9733</t>
-  </si>
-  <si>
-    <t>0.0230,0.0120,0.0014,0.9882</t>
-  </si>
-  <si>
-    <t>0.0041,0.0003,0.0017,0.9966</t>
-  </si>
-  <si>
-    <t>0.0056,0.0030,0.0012,0.9956</t>
-  </si>
-  <si>
-    <t>0.9225,0.0288,0.0177,0.0093</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9281,0.0278,0.0100,0.0136</t>
+  </si>
+  <si>
+    <t>0.1566,0.0038,0.0103,0.9061</t>
+  </si>
+  <si>
+    <t>0.8806,0.0164,0.0101,0.0853</t>
+  </si>
+  <si>
+    <t>0.1301,0.0080,0.0132,0.9357</t>
+  </si>
+  <si>
+    <t>0.9969,0.0007,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9963,0.0017,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9896,0.0068,0.0013,0.0008</t>
+  </si>
+  <si>
+    <t>0.9949,0.0016,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9964,0.0018,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9907,0.0134,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9955,0.0013,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9885,0.0053,0.0011,0.0016</t>
+  </si>
+  <si>
+    <t>0.6638,0.1109,0.2453,0.0091</t>
+  </si>
+  <si>
+    <t>0.3205,0.1094,0.6577,0.0174</t>
+  </si>
+  <si>
+    <t>0.2090,0.0246,0.8327,0.0009</t>
+  </si>
+  <si>
+    <t>0.2573,0.0204,0.7876,0.0064</t>
+  </si>
+  <si>
+    <t>0.5216,0.0388,0.5445,0.0052</t>
+  </si>
+  <si>
+    <t>0.0365,0.9588,0.0073,0.0008</t>
+  </si>
+  <si>
+    <t>0.0028,0.9917,0.0032,0.0008</t>
+  </si>
+  <si>
+    <t>0.0996,0.9063,0.0148,0.0010</t>
+  </si>
+  <si>
+    <t>0.0078,0.9907,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.0016,0.9968,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.2107,0.0062,0.8552,0.0059</t>
+  </si>
+  <si>
+    <t>0.1642,0.0116,0.8889,0.0045</t>
+  </si>
+  <si>
+    <t>0.0841,0.0045,0.9415,0.0036</t>
+  </si>
+  <si>
+    <t>0.0583,0.0036,0.9579,0.0026</t>
+  </si>
+  <si>
+    <t>0.3079,0.0046,0.8332,0.0023</t>
+  </si>
+  <si>
+    <t>0.0288,0.0051,0.9635,0.0072</t>
+  </si>
+  <si>
+    <t>0.0601,0.0066,0.9475,0.0071</t>
+  </si>
+  <si>
+    <t>0.3328,0.7551,0.0052,0.0018</t>
+  </si>
+  <si>
+    <t>0.8337,0.1000,0.0821,0.0148</t>
+  </si>
+  <si>
+    <t>0.0003,0.0029,0.9974,0.0029</t>
+  </si>
+  <si>
+    <t>0.0054,0.8616,0.5693,0.0009</t>
+  </si>
+  <si>
+    <t>0.9222,0.0474,0.0106,0.0084</t>
+  </si>
+  <si>
+    <t>0.3308,0.0392,0.7486,0.0111</t>
+  </si>
+  <si>
+    <t>0.8215,0.2747,0.0064,0.0011</t>
+  </si>
+  <si>
+    <t>0.0146,0.9664,0.0855,0.0012</t>
+  </si>
+  <si>
+    <t>0.0362,0.8073,0.1759,0.0718</t>
+  </si>
+  <si>
+    <t>0.1287,0.2891,0.7505,0.0369</t>
+  </si>
+  <si>
+    <t>0.0750,0.1701,0.8489,0.0202</t>
+  </si>
+  <si>
+    <t>0.0208,0.0043,0.9721,0.0109</t>
+  </si>
+  <si>
+    <t>0.0384,0.1272,0.9294,0.0015</t>
+  </si>
+  <si>
+    <t>0.0068,0.9797,0.0219,0.0008</t>
+  </si>
+  <si>
+    <t>0.0398,0.0150,0.9460,0.0131</t>
+  </si>
+  <si>
+    <t>0.2085,0.6194,0.1014,0.5336</t>
+  </si>
+  <si>
+    <t>0.0028,0.9503,0.0124,0.0721</t>
+  </si>
+  <si>
+    <t>0.0034,0.9823,0.0924,0.0003</t>
+  </si>
+  <si>
+    <t>0.0052,0.9827,0.0143,0.0018</t>
+  </si>
+  <si>
+    <t>0.0413,0.0158,0.9499,0.0022</t>
+  </si>
+  <si>
+    <t>0.0019,0.3461,0.9854,0.0004</t>
+  </si>
+  <si>
+    <t>0.1132,0.0291,0.9037,0.0064</t>
+  </si>
+  <si>
+    <t>0.0667,0.0036,0.9540,0.0018</t>
+  </si>
+  <si>
+    <t>0.0948,0.1756,0.8398,0.0296</t>
+  </si>
+  <si>
+    <t>0.0111,0.0128,0.9737,0.0022</t>
+  </si>
+  <si>
+    <t>0.9683,0.0404,0.0031,0.0010</t>
+  </si>
+  <si>
+    <t>0.9834,0.0091,0.0019,0.0013</t>
+  </si>
+  <si>
+    <t>0.9765,0.0111,0.0021,0.0051</t>
+  </si>
+  <si>
+    <t>0.0079,0.0390,0.9837,0.0027</t>
+  </si>
+  <si>
+    <t>0.9917,0.0050,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.9907,0.0043,0.0008,0.0011</t>
+  </si>
+  <si>
+    <t>0.9514,0.0567,0.0079,0.0018</t>
+  </si>
+  <si>
+    <t>0.0226,0.4181,0.8829,0.0052</t>
+  </si>
+  <si>
+    <t>0.0016,0.0253,0.9742,0.0200</t>
+  </si>
+  <si>
+    <t>0.0101,0.0667,0.9590,0.0155</t>
+  </si>
+  <si>
+    <t>0.0022,0.8466,0.9424,0.0005</t>
+  </si>
+  <si>
+    <t>0.0044,0.0024,0.9932,0.0013</t>
+  </si>
+  <si>
+    <t>0.0294,0.9534,0.0206,0.0013</t>
+  </si>
+  <si>
+    <t>0.0299,0.9698,0.0020,0.0004</t>
+  </si>
+  <si>
+    <t>0.9084,0.0363,0.0246,0.0141</t>
+  </si>
+  <si>
+    <t>0.8696,0.0943,0.0448,0.0074</t>
+  </si>
+  <si>
+    <t>0.0034,0.0131,0.9949,0.0002</t>
+  </si>
+  <si>
+    <t>0.0040,0.8603,0.7142,0.0008</t>
+  </si>
+  <si>
+    <t>0.0021,0.9565,0.5427,0.0005</t>
+  </si>
+  <si>
+    <t>0.0069,0.9215,0.5031,0.0017</t>
+  </si>
+  <si>
+    <t>0.0008,0.9239,0.9292,0.0002</t>
+  </si>
+  <si>
+    <t>0.2379,0.0104,0.1641,0.5992</t>
+  </si>
+  <si>
+    <t>0.0008,0.0058,0.0001,0.9989</t>
+  </si>
+  <si>
+    <t>0.0015,0.1160,0.0002,0.9964</t>
+  </si>
+  <si>
+    <t>0.0268,0.0021,0.0121,0.9754</t>
+  </si>
+  <si>
+    <t>0.0206,0.0047,0.0179,0.9773</t>
+  </si>
+  <si>
+    <t>0.0045,0.0064,0.0051,0.9939</t>
+  </si>
+  <si>
+    <t>0.0015,0.9532,0.8624,0.0003</t>
+  </si>
+  <si>
+    <t>0.0049,0.8200,0.8698,0.0011</t>
+  </si>
+  <si>
+    <t>0.0200,0.4831,0.7655,0.0149</t>
+  </si>
+  <si>
+    <t>0.0100,0.6668,0.6948,0.0049</t>
+  </si>
+  <si>
+    <t>0.0004,0.9942,0.1715,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.8629,0.8669,0.0003</t>
+  </si>
+  <si>
+    <t>0.9937,0.0041,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9873,0.0121,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.9857,0.0117,0.0013,0.0010</t>
+  </si>
+  <si>
+    <t>0.9858,0.0094,0.0008,0.0014</t>
+  </si>
+  <si>
+    <t>0.9752,0.0320,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9922,0.0050,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.9879,0.0033,0.0012,0.0028</t>
+  </si>
+  <si>
+    <t>0.9970,0.0016,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9978,0.0003,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9948,0.0020,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9949,0.0009,0.0001,0.0015</t>
+  </si>
+  <si>
+    <t>0.9933,0.0036,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9912,0.0059,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.9941,0.0033,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9932,0.0018,0.0005,0.0012</t>
+  </si>
+  <si>
+    <t>0.0127,0.0032,0.9901,0.0008</t>
+  </si>
+  <si>
+    <t>0.2320,0.0351,0.8140,0.0053</t>
+  </si>
+  <si>
+    <t>0.8338,0.0067,0.1327,0.0076</t>
+  </si>
+  <si>
+    <t>0.0629,0.0038,0.9425,0.0052</t>
+  </si>
+  <si>
+    <t>0.0530,0.9479,0.0085,0.0006</t>
+  </si>
+  <si>
+    <t>0.1067,0.9135,0.0088,0.0007</t>
+  </si>
+  <si>
+    <t>0.0263,0.9710,0.0011,0.0022</t>
+  </si>
+  <si>
+    <t>0.5660,0.5153,0.0250,0.0035</t>
+  </si>
+  <si>
+    <t>0.2407,0.7834,0.0240,0.0069</t>
+  </si>
+  <si>
+    <t>0.0102,0.9833,0.0021,0.0007</t>
+  </si>
+  <si>
+    <t>0.3251,0.7713,0.0060,0.0013</t>
+  </si>
+  <si>
+    <t>0.5075,0.1855,0.0328,0.3286</t>
+  </si>
+  <si>
+    <t>0.6010,0.0072,0.5515,0.0010</t>
+  </si>
+  <si>
+    <t>0.6524,0.1461,0.2408,0.0146</t>
+  </si>
+  <si>
+    <t>0.5407,0.2351,0.2756,0.0234</t>
+  </si>
+  <si>
+    <t>0.1431,0.0176,0.1244,0.7873</t>
+  </si>
+  <si>
+    <t>0.0040,0.9879,0.0033,0.0009</t>
+  </si>
+  <si>
+    <t>0.0025,0.9749,0.0160,0.0210</t>
+  </si>
+  <si>
+    <t>0.0273,0.9620,0.0069,0.0036</t>
+  </si>
+  <si>
+    <t>0.0003,0.8653,0.9748,0.0001</t>
+  </si>
+  <si>
+    <t>0.0318,0.9535,0.0349,0.0003</t>
+  </si>
+  <si>
+    <t>0.8975,0.1299,0.0156,0.0015</t>
+  </si>
+  <si>
+    <t>0.7177,0.4245,0.0037,0.0005</t>
+  </si>
+  <si>
+    <t>0.9893,0.0049,0.0010,0.0014</t>
+  </si>
+  <si>
+    <t>0.9902,0.0024,0.0007,0.0021</t>
+  </si>
+  <si>
+    <t>0.9925,0.0015,0.0004,0.0017</t>
+  </si>
+  <si>
+    <t>0.9748,0.0183,0.0046,0.0016</t>
+  </si>
+  <si>
+    <t>0.9954,0.0008,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.9659,0.0267,0.0070,0.0023</t>
+  </si>
+  <si>
+    <t>0.9918,0.0025,0.0004,0.0014</t>
+  </si>
+  <si>
+    <t>0.9878,0.0070,0.0013,0.0008</t>
+  </si>
+  <si>
+    <t>0.0027,0.4565,0.9744,0.0005</t>
+  </si>
+  <si>
+    <t>0.0078,0.9365,0.2416,0.0005</t>
+  </si>
+  <si>
+    <t>0.0074,0.6120,0.7487,0.0019</t>
+  </si>
+  <si>
+    <t>0.1037,0.1040,0.8182,0.0061</t>
+  </si>
+  <si>
+    <t>0.7908,0.0567,0.0767,0.0756</t>
+  </si>
+  <si>
+    <t>0.8702,0.0630,0.0524,0.0091</t>
+  </si>
+  <si>
+    <t>0.1407,0.0025,0.9025,0.0053</t>
+  </si>
+  <si>
+    <t>0.6298,0.0276,0.3904,0.0149</t>
+  </si>
+  <si>
+    <t>0.0349,0.0012,0.0018,0.9838</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0008,0.9997</t>
+  </si>
+  <si>
+    <t>0.0025,0.0148,0.0016,0.9959</t>
+  </si>
+  <si>
+    <t>0.0523,0.0022,0.0065,0.9691</t>
+  </si>
+  <si>
+    <t>0.0008,0.8899,0.9484,0.0002</t>
+  </si>
+  <si>
+    <t>0.9661,0.0261,0.0041,0.0024</t>
+  </si>
+  <si>
+    <t>0.8370,0.1389,0.0515,0.0079</t>
+  </si>
+  <si>
+    <t>0.9657,0.0173,0.0036,0.0069</t>
+  </si>
+  <si>
+    <t>0.3703,0.7198,0.0080,0.0009</t>
+  </si>
+  <si>
+    <t>0.9790,0.0015,0.0010,0.0114</t>
+  </si>
+  <si>
+    <t>0.1569,0.0121,0.0107,0.9127</t>
+  </si>
+  <si>
+    <t>0.9819,0.0082,0.0019,0.0022</t>
+  </si>
+  <si>
+    <t>0.0025,0.0306,0.9732,0.0246</t>
+  </si>
+  <si>
+    <t>0.9197,0.0024,0.0105,0.0414</t>
+  </si>
+  <si>
+    <t>0.8527,0.0065,0.0011,0.1152</t>
+  </si>
+  <si>
+    <t>0.7578,0.2285,0.0426,0.0335</t>
+  </si>
+  <si>
+    <t>0.9295,0.0319,0.0176,0.0085</t>
+  </si>
+  <si>
+    <t>0.9404,0.0491,0.0105,0.0021</t>
+  </si>
+  <si>
+    <t>0.5404,0.4100,0.0968,0.0519</t>
+  </si>
+  <si>
+    <t>0.8114,0.0821,0.1029,0.0122</t>
+  </si>
+  <si>
+    <t>0.8806,0.1374,0.0187,0.0008</t>
+  </si>
+  <si>
+    <t>0.9922,0.0038,0.0013,0.0005</t>
+  </si>
+  <si>
+    <t>0.9799,0.0058,0.0022,0.0055</t>
+  </si>
+  <si>
+    <t>0.9924,0.0028,0.0008,0.0008</t>
+  </si>
+  <si>
+    <t>0.9955,0.0009,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9875,0.0074,0.0010,0.0009</t>
+  </si>
+  <si>
+    <t>0.9758,0.0190,0.0025,0.0013</t>
+  </si>
+  <si>
+    <t>0.9825,0.0090,0.0025,0.0022</t>
+  </si>
+  <si>
+    <t>0.9893,0.0028,0.0004,0.0024</t>
+  </si>
+  <si>
+    <t>0.4199,0.6454,0.0019,0.0021</t>
+  </si>
+  <si>
+    <t>0.5562,0.6013,0.0015,0.0007</t>
+  </si>
+  <si>
+    <t>0.6542,0.5088,0.0019,0.0005</t>
+  </si>
+  <si>
+    <t>0.2561,0.1825,0.7135,0.0071</t>
+  </si>
+  <si>
+    <t>0.9712,0.0337,0.0025,0.0009</t>
+  </si>
+  <si>
+    <t>0.9267,0.0803,0.0109,0.0060</t>
+  </si>
+  <si>
+    <t>0.9362,0.0977,0.0056,0.0012</t>
+  </si>
+  <si>
+    <t>0.9191,0.1023,0.0078,0.0013</t>
+  </si>
+  <si>
+    <t>0.0086,0.0143,0.9917,0.0003</t>
+  </si>
+  <si>
+    <t>0.9444,0.0709,0.0064,0.0011</t>
+  </si>
+  <si>
+    <t>0.0053,0.0021,0.9921,0.0019</t>
+  </si>
+  <si>
+    <t>0.0097,0.0351,0.9421,0.0337</t>
+  </si>
+  <si>
+    <t>0.1357,0.0073,0.9090,0.0038</t>
+  </si>
+  <si>
+    <t>0.0917,0.2168,0.7805,0.0086</t>
+  </si>
+  <si>
+    <t>0.0655,0.0046,0.9550,0.0026</t>
+  </si>
+  <si>
+    <t>0.0444,0.0059,0.9768,0.0002</t>
+  </si>
+  <si>
+    <t>0.0531,0.0215,0.9348,0.0046</t>
+  </si>
+  <si>
+    <t>0.4271,0.0804,0.5413,0.0583</t>
+  </si>
+  <si>
+    <t>0.5590,0.1460,0.1557,0.0007</t>
+  </si>
+  <si>
+    <t>0.2379,0.0301,0.7955,0.0134</t>
+  </si>
+  <si>
+    <t>0.3188,0.1128,0.5586,0.0077</t>
+  </si>
+  <si>
+    <t>0.1215,0.1029,0.7513,0.0006</t>
+  </si>
+  <si>
+    <t>0.3073,0.1236,0.5338,0.0072</t>
+  </si>
+  <si>
+    <t>0.4484,0.3973,0.2569,0.0472</t>
+  </si>
+  <si>
+    <t>0.1765,0.1280,0.7365,0.0287</t>
+  </si>
+  <si>
+    <t>0.5183,0.6543,0.0014,0.0008</t>
+  </si>
+  <si>
+    <t>0.3009,0.8297,0.0021,0.0003</t>
+  </si>
+  <si>
+    <t>0.4361,0.7045,0.0019,0.0006</t>
+  </si>
+  <si>
+    <t>0.9697,0.0442,0.0021,0.0007</t>
+  </si>
+  <si>
+    <t>0.5430,0.5843,0.0049,0.0033</t>
+  </si>
+  <si>
+    <t>0.7851,0.0328,0.1222,0.0642</t>
+  </si>
+  <si>
+    <t>0.8321,0.0221,0.1378,0.0062</t>
+  </si>
+  <si>
+    <t>0.7510,0.0102,0.1959,0.0222</t>
+  </si>
+  <si>
+    <t>0.2222,0.0301,0.8132,0.0128</t>
+  </si>
+  <si>
+    <t>0.7355,0.0547,0.2117,0.0184</t>
+  </si>
+  <si>
+    <t>0.0983,0.0052,0.9140,0.0132</t>
+  </si>
+  <si>
+    <t>0.0297,0.3952,0.7572,0.0053</t>
+  </si>
+  <si>
+    <t>0.0079,0.2804,0.9630,0.0018</t>
+  </si>
+  <si>
+    <t>0.0490,0.0845,0.9160,0.0080</t>
+  </si>
+  <si>
+    <t>0.0214,0.2525,0.8290,0.0025</t>
+  </si>
+  <si>
+    <t>0.9821,0.0133,0.0028,0.0015</t>
+  </si>
+  <si>
+    <t>0.9881,0.0092,0.0020,0.0006</t>
+  </si>
+  <si>
+    <t>0.9905,0.0086,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9771,0.0473,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9885,0.0051,0.0007,0.0018</t>
+  </si>
+  <si>
+    <t>0.9782,0.0261,0.0017,0.0008</t>
+  </si>
+  <si>
+    <t>0.9854,0.0112,0.0003,0.0012</t>
+  </si>
+  <si>
+    <t>0.9955,0.0017,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.1092,0.0043,0.9291,0.0028</t>
+  </si>
+  <si>
+    <t>0.5374,0.2918,0.3029,0.0415</t>
+  </si>
+  <si>
+    <t>0.7250,0.0119,0.3645,0.0024</t>
+  </si>
+  <si>
+    <t>0.0195,0.0011,0.9819,0.0021</t>
+  </si>
+  <si>
+    <t>0.0013,0.0355,0.9922,0.0008</t>
+  </si>
+  <si>
+    <t>0.0495,0.0132,0.9541,0.0040</t>
+  </si>
+  <si>
+    <t>0.0016,0.0083,0.9961,0.0010</t>
+  </si>
+  <si>
+    <t>0.0399,0.0094,0.9667,0.0004</t>
+  </si>
+  <si>
+    <t>0.0044,0.0267,0.9912,0.0003</t>
+  </si>
+  <si>
+    <t>0.0129,0.0101,0.9702,0.0067</t>
+  </si>
+  <si>
+    <t>0.3836,0.0750,0.5936,0.0050</t>
+  </si>
+  <si>
+    <t>0.6975,0.1106,0.2153,0.0213</t>
+  </si>
+  <si>
+    <t>0.7515,0.0082,0.3493,0.0018</t>
+  </si>
+  <si>
+    <t>0.8333,0.0711,0.0895,0.0055</t>
+  </si>
+  <si>
+    <t>0.9896,0.0066,0.0004,0.0015</t>
+  </si>
+  <si>
+    <t>0.9767,0.0258,0.0013,0.0011</t>
+  </si>
+  <si>
+    <t>0.9906,0.0081,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.9953,0.0025,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9939,0.0016,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.9876,0.0118,0.0013,0.0006</t>
+  </si>
+  <si>
+    <t>0.9897,0.0084,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9870,0.0142,0.0014,0.0004</t>
+  </si>
+  <si>
+    <t>0.0205,0.1621,0.8718,0.0022</t>
+  </si>
+  <si>
+    <t>0.0062,0.0418,0.9859,0.0013</t>
+  </si>
+  <si>
+    <t>0.0564,0.0512,0.9065,0.0253</t>
+  </si>
+  <si>
+    <t>0.3470,0.0486,0.6072,0.0049</t>
+  </si>
+  <si>
+    <t>0.0092,0.0043,0.9883,0.0014</t>
+  </si>
+  <si>
+    <t>0.1645,0.0355,0.7816,0.0766</t>
+  </si>
+  <si>
+    <t>0.2354,0.0228,0.7608,0.0326</t>
+  </si>
+  <si>
+    <t>0.0175,0.0248,0.9606,0.0159</t>
+  </si>
+  <si>
+    <t>0.9713,0.0014,0.0022,0.0213</t>
+  </si>
+  <si>
+    <t>0.0146,0.0624,0.0021,0.9851</t>
+  </si>
+  <si>
+    <t>0.0301,0.0099,0.0022,0.9850</t>
+  </si>
+  <si>
+    <t>0.0062,0.0026,0.0082,0.9927</t>
+  </si>
+  <si>
+    <t>0.0028,0.0009,0.0003,0.9985</t>
+  </si>
+  <si>
+    <t>0.8157,0.0341,0.0314,0.1104</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1993,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2133,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2158,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,10 +2186,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2231,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2270,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2287,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2368,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2382,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2410,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,10 +2438,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2455,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2483,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,10 +2522,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2807,10 +2816,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2917,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2931,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2959,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2970,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,10 +2984,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3001,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3113,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3124,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3138,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,10 +3152,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3169,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>272</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,10 +3502,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3544,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3561,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,10 +3572,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3589,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3603,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3617,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3673,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3715,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3838,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3852,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,10 +3866,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3925,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4009,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4034,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4065,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,10 +4090,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,10 +4160,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4202,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4356,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4370,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4384,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4398,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4594,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4608,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4625,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4639,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4653,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4667,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4678,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4695,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4706,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4723,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4725,10 +4734,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,10 +4762,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4779,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4807,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4818,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4905,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,7 +5045,7 @@
         <v>259</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5199,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5406,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5451,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5521,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
